--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.02172980679389</v>
+        <v>6.178531093604007</v>
       </c>
       <c r="D2" t="n">
-        <v>38.47281779078474</v>
+        <v>6.25183289100252</v>
       </c>
       <c r="E2" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F2" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.60343358439282</v>
+        <v>2.698057957463833</v>
       </c>
       <c r="D3" t="n">
-        <v>16.50872103058251</v>
+        <v>2.682667167469658</v>
       </c>
       <c r="E3" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F3" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.6815410933618</v>
+        <v>7.260750427671293</v>
       </c>
       <c r="D4" t="n">
-        <v>44.99033479107877</v>
+        <v>7.310929403550301</v>
       </c>
       <c r="E4" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F4" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.84567116701811</v>
+        <v>5.824921564640444</v>
       </c>
       <c r="D5" t="n">
-        <v>36.09192659059568</v>
+        <v>5.864938070971799</v>
       </c>
       <c r="E5" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F5" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.28338474634681</v>
+        <v>3.783550021281357</v>
       </c>
       <c r="D6" t="n">
-        <v>24.06533653215259</v>
+        <v>3.910617186474795</v>
       </c>
       <c r="E6" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F6" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.85123226541582</v>
+        <v>7.450825243130072</v>
       </c>
       <c r="D7" t="n">
-        <v>48.0415228683063</v>
+        <v>7.806747466099774</v>
       </c>
       <c r="E7" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F7" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.56316225185753</v>
+        <v>6.75401386592685</v>
       </c>
       <c r="D8" t="n">
-        <v>31.91046501976707</v>
+        <v>5.185450565712149</v>
       </c>
       <c r="E8" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F8" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.37930935744996</v>
+        <v>7.861637770585619</v>
       </c>
       <c r="D9" t="n">
-        <v>31.4379368406762</v>
+        <v>5.108664736609883</v>
       </c>
       <c r="E9" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F9" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.71097613174273</v>
+        <v>5.153033621408194</v>
       </c>
       <c r="D10" t="n">
-        <v>18.9165483453575</v>
+        <v>3.073939106120593</v>
       </c>
       <c r="E10" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F10" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.70299339415753</v>
+        <v>6.451736426550599</v>
       </c>
       <c r="D11" t="n">
-        <v>8.12039862112788</v>
+        <v>1.31956477593328</v>
       </c>
       <c r="E11" t="n">
-        <v>9.631123297162807</v>
+        <v>1.565057535788956</v>
       </c>
       <c r="F11" t="n">
-        <v>12.17953455197656</v>
+        <v>1.979174364696191</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
